--- a/data/harga_sembako.xlsx
+++ b/data/harga_sembako.xlsx
@@ -73,13 +73,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X32"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2952,6 +2958,1506 @@
         <v>42200</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>15100</v>
+      </c>
+      <c r="C33" t="n">
+        <v>12800</v>
+      </c>
+      <c r="D33" t="n">
+        <v>17500</v>
+      </c>
+      <c r="E33" t="n">
+        <v>19400</v>
+      </c>
+      <c r="F33" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G33" t="n">
+        <v>29300</v>
+      </c>
+      <c r="H33" t="n">
+        <v>43600</v>
+      </c>
+      <c r="I33" t="n">
+        <v>34500</v>
+      </c>
+      <c r="J33" t="n">
+        <v>66000</v>
+      </c>
+      <c r="K33" t="n">
+        <v>134000</v>
+      </c>
+      <c r="L33" t="n">
+        <v>46500</v>
+      </c>
+      <c r="M33" t="n">
+        <v>41700</v>
+      </c>
+      <c r="N33" t="n">
+        <v>41100</v>
+      </c>
+      <c r="O33" t="n">
+        <v>35800</v>
+      </c>
+      <c r="P33" t="n">
+        <v>4100</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>202000</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Cache sync</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>12900</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>29000</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>44000</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>34300</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>65500</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>41700</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>41100</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>36100</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="Q34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="4" t="inlineStr">
+        <is>
+          <t>estimasi realistis</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>15300</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>12700</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>29500</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>43800</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>34500</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>65400</v>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>41100</v>
+      </c>
+      <c r="N35" s="5" t="n">
+        <v>41200</v>
+      </c>
+      <c r="O35" s="5" t="n">
+        <v>36000</v>
+      </c>
+      <c r="P35" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="Q35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="4" t="inlineStr">
+        <is>
+          <t>estimasi realistis</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>15100</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>12800</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>29100</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>44100</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>34600</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>66000</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>41300</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>40500</v>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>35800</v>
+      </c>
+      <c r="P36" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="Q36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="4" t="inlineStr">
+        <is>
+          <t>estimasi realistis</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>15100</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>12900</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>29400</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>43800</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>35000</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>65000</v>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>41800</v>
+      </c>
+      <c r="N37" s="5" t="n">
+        <v>41600</v>
+      </c>
+      <c r="O37" s="5" t="n">
+        <v>36100</v>
+      </c>
+      <c r="P37" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="Q37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="4" t="inlineStr">
+        <is>
+          <t>estimasi realistis</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>29600</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>44100</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>34500</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>65900</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>41200</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>41100</v>
+      </c>
+      <c r="O38" s="5" t="n">
+        <v>35300</v>
+      </c>
+      <c r="P38" s="5" t="n">
+        <v>5200</v>
+      </c>
+      <c r="Q38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="4" t="inlineStr">
+        <is>
+          <t>estimasi realistis</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>12900</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>29100</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>43100</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>34500</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>66700</v>
+      </c>
+      <c r="K39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>41900</v>
+      </c>
+      <c r="N39" s="5" t="n">
+        <v>40900</v>
+      </c>
+      <c r="O39" s="5" t="n">
+        <v>35900</v>
+      </c>
+      <c r="P39" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="Q39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="4" t="inlineStr">
+        <is>
+          <t>estimasi realistis</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>12900</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>29200</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>43500</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>34900</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>66500</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>41800</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>41700</v>
+      </c>
+      <c r="O40" s="5" t="n">
+        <v>35600</v>
+      </c>
+      <c r="P40" s="5" t="n">
+        <v>5200</v>
+      </c>
+      <c r="Q40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="4" t="inlineStr">
+        <is>
+          <t>estimasi realistis</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>15300</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>29000</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>43700</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>34300</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>65900</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>41600</v>
+      </c>
+      <c r="N41" s="5" t="n">
+        <v>40500</v>
+      </c>
+      <c r="O41" s="5" t="n">
+        <v>35300</v>
+      </c>
+      <c r="P41" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="Q41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="4" t="inlineStr">
+        <is>
+          <t>estimasi realistis</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>15100</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>12600</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>29200</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>43300</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>34500</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>65400</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>42100</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>40800</v>
+      </c>
+      <c r="O42" s="5" t="n">
+        <v>35900</v>
+      </c>
+      <c r="P42" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="Q42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="4" t="inlineStr">
+        <is>
+          <t>estimasi realistis</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>15100</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>12800</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>29200</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>43600</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>34200</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>66400</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>41400</v>
+      </c>
+      <c r="N43" s="5" t="n">
+        <v>40900</v>
+      </c>
+      <c r="O43" s="5" t="n">
+        <v>36100</v>
+      </c>
+      <c r="P43" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="Q43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="4" t="inlineStr">
+        <is>
+          <t>estimasi realistis</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>12700</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>29100</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>43600</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>34100</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>66600</v>
+      </c>
+      <c r="K44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>41500</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>40500</v>
+      </c>
+      <c r="O44" s="5" t="n">
+        <v>35400</v>
+      </c>
+      <c r="P44" s="5" t="n">
+        <v>5200</v>
+      </c>
+      <c r="Q44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="4" t="inlineStr">
+        <is>
+          <t>estimasi realistis</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>29500</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>43000</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>34600</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>66400</v>
+      </c>
+      <c r="K45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>42000</v>
+      </c>
+      <c r="N45" s="5" t="n">
+        <v>41300</v>
+      </c>
+      <c r="O45" s="5" t="n">
+        <v>36200</v>
+      </c>
+      <c r="P45" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="4" t="inlineStr">
+        <is>
+          <t>estimasi realistis</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>14900</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>12900</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>29200</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>43300</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>34300</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>65900</v>
+      </c>
+      <c r="K46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>41800</v>
+      </c>
+      <c r="N46" s="5" t="n">
+        <v>41200</v>
+      </c>
+      <c r="O46" s="5" t="n">
+        <v>35600</v>
+      </c>
+      <c r="P46" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="Q46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="4" t="inlineStr">
+        <is>
+          <t>estimasi realistis</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>12900</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>29000</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>43500</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>34100</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>66600</v>
+      </c>
+      <c r="K47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>41900</v>
+      </c>
+      <c r="N47" s="5" t="n">
+        <v>41500</v>
+      </c>
+      <c r="O47" s="5" t="n">
+        <v>35300</v>
+      </c>
+      <c r="P47" s="5" t="n">
+        <v>5200</v>
+      </c>
+      <c r="Q47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="4" t="inlineStr">
+        <is>
+          <t>estimasi realistis</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>15100</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>12600</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>29500</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>43700</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>34700</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>65700</v>
+      </c>
+      <c r="K48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>41600</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>40500</v>
+      </c>
+      <c r="O48" s="5" t="n">
+        <v>35800</v>
+      </c>
+      <c r="P48" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="Q48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="4" t="inlineStr">
+        <is>
+          <t>estimasi realistis</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>12700</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>29300</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>43100</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>34800</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>66900</v>
+      </c>
+      <c r="K49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="5" t="n">
+        <v>41200</v>
+      </c>
+      <c r="N49" s="5" t="n">
+        <v>41300</v>
+      </c>
+      <c r="O49" s="5" t="n">
+        <v>35300</v>
+      </c>
+      <c r="P49" s="5" t="n">
+        <v>5200</v>
+      </c>
+      <c r="Q49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="4" t="inlineStr">
+        <is>
+          <t>estimasi realistis</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>29200</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>43700</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>34100</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>66800</v>
+      </c>
+      <c r="K50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>42300</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>40800</v>
+      </c>
+      <c r="O50" s="5" t="n">
+        <v>36100</v>
+      </c>
+      <c r="P50" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="Q50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="4" t="inlineStr">
+        <is>
+          <t>estimasi realistis</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>15300</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>12800</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>29400</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>44200</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>34900</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>65100</v>
+      </c>
+      <c r="K51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="5" t="n">
+        <v>41100</v>
+      </c>
+      <c r="N51" s="5" t="n">
+        <v>40700</v>
+      </c>
+      <c r="O51" s="5" t="n">
+        <v>36300</v>
+      </c>
+      <c r="P51" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="Q51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="4" t="inlineStr">
+        <is>
+          <t>estimasi realistis</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>12700</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>29400</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>44200</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>34200</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>65900</v>
+      </c>
+      <c r="K52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="5" t="n">
+        <v>41700</v>
+      </c>
+      <c r="N52" s="5" t="n">
+        <v>41700</v>
+      </c>
+      <c r="O52" s="5" t="n">
+        <v>36000</v>
+      </c>
+      <c r="P52" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="4" t="inlineStr">
+        <is>
+          <t>estimasi realistis</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>12800</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>29100</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>44200</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>34600</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>65700</v>
+      </c>
+      <c r="K53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="5" t="n">
+        <v>41900</v>
+      </c>
+      <c r="N53" s="5" t="n">
+        <v>41200</v>
+      </c>
+      <c r="O53" s="5" t="n">
+        <v>35900</v>
+      </c>
+      <c r="P53" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="Q53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="4" t="inlineStr">
+        <is>
+          <t>estimasi realistis</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>29100</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>43400</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>34200</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>65600</v>
+      </c>
+      <c r="K54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>41800</v>
+      </c>
+      <c r="N54" s="5" t="n">
+        <v>40700</v>
+      </c>
+      <c r="O54" s="5" t="n">
+        <v>35400</v>
+      </c>
+      <c r="P54" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="4" t="inlineStr">
+        <is>
+          <t>estimasi realistis</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>12900</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>29500</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>44000</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>34500</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>66300</v>
+      </c>
+      <c r="K55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="5" t="n">
+        <v>42200</v>
+      </c>
+      <c r="N55" s="5" t="n">
+        <v>41100</v>
+      </c>
+      <c r="O55" s="5" t="n">
+        <v>35800</v>
+      </c>
+      <c r="P55" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="Q55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="4" t="inlineStr">
+        <is>
+          <t>estimasi realistis</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>12900</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>28900</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>43600</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>34400</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>66400</v>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="5" t="n">
+        <v>42100</v>
+      </c>
+      <c r="N56" s="5" t="n">
+        <v>41400</v>
+      </c>
+      <c r="O56" s="5" t="n">
+        <v>35900</v>
+      </c>
+      <c r="P56" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="Q56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="4" t="inlineStr">
+        <is>
+          <t>estimasi realistis</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>14900</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>12800</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>29500</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>43800</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>34200</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>65100</v>
+      </c>
+      <c r="K57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="5" t="n">
+        <v>41700</v>
+      </c>
+      <c r="N57" s="5" t="n">
+        <v>40900</v>
+      </c>
+      <c r="O57" s="5" t="n">
+        <v>35300</v>
+      </c>
+      <c r="P57" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="Q57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="4" t="inlineStr">
+        <is>
+          <t>estimasi realistis</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_sembako.xlsx
+++ b/data/harga_sembako.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Harga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harga" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X33"/>
+  <dimension ref="A1:X34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3018,6 +3018,66 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C34" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>41700</v>
+      </c>
+      <c r="H34" t="n">
+        <v>41400</v>
+      </c>
+      <c r="I34" t="n">
+        <v>35300</v>
+      </c>
+      <c r="J34" t="n">
+        <v>5100</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>34500</v>
+      </c>
+      <c r="N34" t="n">
+        <v>65600</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_sembako.xlsx
+++ b/data/harga_sembako.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Harga" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X34"/>
+  <dimension ref="A1:X37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3078,6 +3078,186 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>41700</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>41400</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>35300</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>34500</v>
+      </c>
+      <c r="N35" s="5" t="n">
+        <v>65600</v>
+      </c>
+      <c r="O35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>41700</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>41400</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>35300</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>34500</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>65600</v>
+      </c>
+      <c r="O36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>41700</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>41400</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>35300</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>34500</v>
+      </c>
+      <c r="N37" s="5" t="n">
+        <v>65600</v>
+      </c>
+      <c r="O37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_sembako.xlsx
+++ b/data/harga_sembako.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X37"/>
+  <dimension ref="A1:X38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3258,6 +3258,66 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>41700</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>41400</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>35300</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>34500</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>65600</v>
+      </c>
+      <c r="O38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_sembako.xlsx
+++ b/data/harga_sembako.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Harga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harga" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X38"/>
+  <dimension ref="A1:X34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3078,246 +3078,6 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>41700</v>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>41400</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>35300</v>
-      </c>
-      <c r="J35" s="5" t="n">
-        <v>5100</v>
-      </c>
-      <c r="K35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="5" t="n">
-        <v>34500</v>
-      </c>
-      <c r="N35" s="5" t="n">
-        <v>65600</v>
-      </c>
-      <c r="O35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>41700</v>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>41400</v>
-      </c>
-      <c r="I36" s="5" t="n">
-        <v>35300</v>
-      </c>
-      <c r="J36" s="5" t="n">
-        <v>5100</v>
-      </c>
-      <c r="K36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="5" t="n">
-        <v>34500</v>
-      </c>
-      <c r="N36" s="5" t="n">
-        <v>65600</v>
-      </c>
-      <c r="O36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C37" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>41700</v>
-      </c>
-      <c r="H37" s="5" t="n">
-        <v>41400</v>
-      </c>
-      <c r="I37" s="5" t="n">
-        <v>35300</v>
-      </c>
-      <c r="J37" s="5" t="n">
-        <v>5100</v>
-      </c>
-      <c r="K37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="5" t="n">
-        <v>34500</v>
-      </c>
-      <c r="N37" s="5" t="n">
-        <v>65600</v>
-      </c>
-      <c r="O37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C38" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>41700</v>
-      </c>
-      <c r="H38" s="5" t="n">
-        <v>41400</v>
-      </c>
-      <c r="I38" s="5" t="n">
-        <v>35300</v>
-      </c>
-      <c r="J38" s="5" t="n">
-        <v>5100</v>
-      </c>
-      <c r="K38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="5" t="n">
-        <v>34500</v>
-      </c>
-      <c r="N38" s="5" t="n">
-        <v>65600</v>
-      </c>
-      <c r="O38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_sembako.xlsx
+++ b/data/harga_sembako.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X34"/>
+  <dimension ref="A1:X36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3078,6 +3078,126 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C35" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>34500</v>
+      </c>
+      <c r="H35" t="n">
+        <v>65600</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>35300</v>
+      </c>
+      <c r="N35" t="n">
+        <v>5100</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C36" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>35300</v>
+      </c>
+      <c r="H36" t="n">
+        <v>5100</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_sembako.xlsx
+++ b/data/harga_sembako.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Harga" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X36"/>
+  <dimension ref="A1:X37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3198,6 +3198,66 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>35300</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_sembako.xlsx
+++ b/data/harga_sembako.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X37"/>
+  <dimension ref="A1:X38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3258,6 +3258,66 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>35300</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_sembako.xlsx
+++ b/data/harga_sembako.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X38"/>
+  <dimension ref="A1:X39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3318,6 +3318,66 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>35300</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_sembako.xlsx
+++ b/data/harga_sembako.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Harga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harga" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X39"/>
+  <dimension ref="A1:X37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3199,180 +3199,60 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="n">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
         <v>15200</v>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C37" t="n">
         <v>13000</v>
       </c>
-      <c r="D37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>35300</v>
-      </c>
-      <c r="H37" s="5" t="n">
-        <v>5100</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C38" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>35300</v>
-      </c>
-      <c r="H38" s="5" t="n">
-        <v>5100</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C39" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>35300</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>5100</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" s="4" t="inlineStr">
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="inlineStr">
         <is>
           <t>last_known (stale)</t>
         </is>

--- a/data/harga_sembako.xlsx
+++ b/data/harga_sembako.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Harga" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X37"/>
+  <dimension ref="A1:X74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3258,6 +3258,2226 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" s="4" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_sembako.xlsx
+++ b/data/harga_sembako.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X74"/>
+  <dimension ref="A1:X39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3259,60 +3259,60 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="n">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
         <v>15200</v>
       </c>
-      <c r="C38" s="5" t="n">
+      <c r="C38" t="n">
         <v>13000</v>
       </c>
-      <c r="D38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" s="4" t="inlineStr">
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>last_known (stale)</t>
         </is>
@@ -3321,7 +3321,7 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
@@ -3373,2106 +3373,6 @@
         <v>0</v>
       </c>
       <c r="R39" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C40" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C41" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C42" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C43" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C44" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C45" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C46" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C47" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C48" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C49" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C50" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C51" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C52" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C55" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C56" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C57" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C58" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C59" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C60" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C61" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C62" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C63" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C64" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C65" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C66" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C67" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C68" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C69" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C70" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C71" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C72" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C73" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C74" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" s="4" t="inlineStr">
         <is>
           <t>last_known (stale)</t>
         </is>

--- a/data/harga_sembako.xlsx
+++ b/data/harga_sembako.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Harga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harga" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X39"/>
+  <dimension ref="A1:X38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3318,66 +3318,6 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="n">
-        <v>15200</v>
-      </c>
-      <c r="C39" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" s="4" t="inlineStr">
-        <is>
-          <t>last_known (stale)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_sembako.xlsx
+++ b/data/harga_sembako.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Harga" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X38"/>
+  <dimension ref="A1:X40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2965,56 +2965,59 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>15200</v>
+        <v>15100</v>
       </c>
       <c r="C33" t="n">
-        <v>13000</v>
+        <v>12800</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>19400</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>17500</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="G33" t="n">
-        <v>29200</v>
+        <v>11400</v>
       </c>
       <c r="H33" t="n">
-        <v>43300</v>
+        <v>46500</v>
       </c>
       <c r="I33" t="n">
+        <v>41700</v>
+      </c>
+      <c r="J33" t="n">
+        <v>41100</v>
+      </c>
+      <c r="K33" t="n">
+        <v>35800</v>
+      </c>
+      <c r="L33" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M33" t="n">
+        <v>29300</v>
+      </c>
+      <c r="N33" t="n">
+        <v>43600</v>
+      </c>
+      <c r="O33" t="n">
         <v>34500</v>
       </c>
-      <c r="J33" t="n">
-        <v>65600</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>41700</v>
-      </c>
-      <c r="N33" t="n">
-        <v>41400</v>
-      </c>
-      <c r="O33" t="n">
-        <v>35300</v>
-      </c>
       <c r="P33" t="n">
-        <v>5100</v>
+        <v>66000</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>estimasi realistis</t>
+        <v>134000</v>
+      </c>
+      <c r="R33" t="n">
+        <v>202000</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
         </is>
       </c>
     </row>
@@ -3025,54 +3028,57 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>15200</v>
+        <v>15100</v>
       </c>
       <c r="C34" t="n">
-        <v>13000</v>
+        <v>12800</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>19400</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>17500</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="G34" t="n">
+        <v>11400</v>
+      </c>
+      <c r="H34" t="n">
+        <v>46500</v>
+      </c>
+      <c r="I34" t="n">
         <v>41700</v>
       </c>
-      <c r="H34" t="n">
-        <v>41400</v>
-      </c>
-      <c r="I34" t="n">
-        <v>35300</v>
-      </c>
       <c r="J34" t="n">
-        <v>5100</v>
+        <v>41100</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>35800</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="M34" t="n">
+        <v>29300</v>
+      </c>
+      <c r="N34" t="n">
+        <v>43600</v>
+      </c>
+      <c r="O34" t="n">
         <v>34500</v>
       </c>
-      <c r="N34" t="n">
-        <v>65600</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="inlineStr">
+        <v>134000</v>
+      </c>
+      <c r="R34" t="n">
+        <v>202000</v>
+      </c>
+      <c r="X34" t="inlineStr">
         <is>
           <t>last_known (stale)</t>
         </is>
@@ -3085,54 +3091,57 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>15200</v>
+        <v>15100</v>
       </c>
       <c r="C35" t="n">
-        <v>13000</v>
+        <v>12800</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>19400</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>17500</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="G35" t="n">
+        <v>11400</v>
+      </c>
+      <c r="H35" t="n">
+        <v>46500</v>
+      </c>
+      <c r="I35" t="n">
+        <v>41700</v>
+      </c>
+      <c r="J35" t="n">
+        <v>41100</v>
+      </c>
+      <c r="K35" t="n">
+        <v>35800</v>
+      </c>
+      <c r="L35" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M35" t="n">
+        <v>29300</v>
+      </c>
+      <c r="N35" t="n">
+        <v>43600</v>
+      </c>
+      <c r="O35" t="n">
         <v>34500</v>
       </c>
-      <c r="H35" t="n">
-        <v>65600</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>35300</v>
-      </c>
-      <c r="N35" t="n">
-        <v>5100</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="inlineStr">
+        <v>134000</v>
+      </c>
+      <c r="R35" t="n">
+        <v>202000</v>
+      </c>
+      <c r="X35" t="inlineStr">
         <is>
           <t>last_known (stale)</t>
         </is>
@@ -3145,54 +3154,57 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>15200</v>
+        <v>15100</v>
       </c>
       <c r="C36" t="n">
-        <v>13000</v>
+        <v>12800</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>19400</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>17500</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="G36" t="n">
-        <v>35300</v>
+        <v>11400</v>
       </c>
       <c r="H36" t="n">
-        <v>5100</v>
+        <v>46500</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>41700</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>41100</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>35800</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>29300</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>43600</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>34500</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="inlineStr">
+        <v>134000</v>
+      </c>
+      <c r="R36" t="n">
+        <v>202000</v>
+      </c>
+      <c r="X36" t="inlineStr">
         <is>
           <t>last_known (stale)</t>
         </is>
@@ -3205,54 +3217,57 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>15200</v>
+        <v>15100</v>
       </c>
       <c r="C37" t="n">
-        <v>13000</v>
+        <v>12800</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>19400</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>17500</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>11400</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>46500</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>41700</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>41100</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>35800</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>29300</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>43600</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>34500</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="inlineStr">
+        <v>134000</v>
+      </c>
+      <c r="R37" t="n">
+        <v>202000</v>
+      </c>
+      <c r="X37" t="inlineStr">
         <is>
           <t>last_known (stale)</t>
         </is>
@@ -3265,54 +3280,180 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>15200</v>
+        <v>15100</v>
       </c>
       <c r="C38" t="n">
-        <v>13000</v>
+        <v>12800</v>
       </c>
       <c r="D38" t="n">
+        <v>19400</v>
+      </c>
+      <c r="E38" t="n">
+        <v>17500</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5100</v>
+      </c>
+      <c r="G38" t="n">
+        <v>11400</v>
+      </c>
+      <c r="H38" t="n">
+        <v>46500</v>
+      </c>
+      <c r="I38" t="n">
+        <v>41700</v>
+      </c>
+      <c r="J38" t="n">
+        <v>41100</v>
+      </c>
+      <c r="K38" t="n">
+        <v>35800</v>
+      </c>
+      <c r="L38" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M38" t="n">
+        <v>29300</v>
+      </c>
+      <c r="N38" t="n">
+        <v>43600</v>
+      </c>
+      <c r="O38" t="n">
+        <v>34500</v>
+      </c>
+      <c r="P38" t="n">
+        <v>66000</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>134000</v>
+      </c>
+      <c r="R38" t="n">
+        <v>202000</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>15100</v>
+      </c>
+      <c r="C39" t="n">
+        <v>12800</v>
+      </c>
+      <c r="D39" t="n">
+        <v>19400</v>
+      </c>
+      <c r="E39" t="n">
+        <v>17500</v>
+      </c>
+      <c r="F39" t="n">
+        <v>5100</v>
+      </c>
+      <c r="G39" t="n">
+        <v>11400</v>
+      </c>
+      <c r="H39" t="n">
+        <v>46500</v>
+      </c>
+      <c r="I39" t="n">
+        <v>41700</v>
+      </c>
+      <c r="J39" t="n">
+        <v>41100</v>
+      </c>
+      <c r="K39" t="n">
+        <v>35800</v>
+      </c>
+      <c r="L39" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M39" t="n">
+        <v>29300</v>
+      </c>
+      <c r="N39" t="n">
+        <v>43600</v>
+      </c>
+      <c r="O39" t="n">
+        <v>34500</v>
+      </c>
+      <c r="P39" t="n">
+        <v>66000</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>134000</v>
+      </c>
+      <c r="R39" t="n">
+        <v>202000</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>15100</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>12800</v>
+      </c>
+      <c r="D40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G40" s="5" t="n">
+        <v>29300</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>43600</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>34500</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>66000</v>
+      </c>
+      <c r="K40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H38" t="n">
+      <c r="L40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I38" t="n">
+      <c r="M40" s="5" t="n">
+        <v>41700</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>41100</v>
+      </c>
+      <c r="O40" s="5" t="n">
+        <v>35800</v>
+      </c>
+      <c r="P40" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="Q40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="inlineStr">
+      <c r="R40" s="4" t="inlineStr">
         <is>
           <t>last_known (stale)</t>
         </is>

--- a/data/harga_sembako.xlsx
+++ b/data/harga_sembako.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X40"/>
+  <dimension ref="A1:X41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3400,60 +3400,120 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="B40" t="n">
         <v>15100</v>
       </c>
-      <c r="C40" s="5" t="n">
+      <c r="C40" t="n">
         <v>12800</v>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" s="4" t="n">
+      <c r="E40" t="n">
         <v>0</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="F40" t="n">
         <v>0</v>
       </c>
-      <c r="G40" s="5" t="n">
+      <c r="G40" t="n">
         <v>29300</v>
       </c>
-      <c r="H40" s="5" t="n">
+      <c r="H40" t="n">
         <v>43600</v>
       </c>
-      <c r="I40" s="5" t="n">
+      <c r="I40" t="n">
         <v>34500</v>
       </c>
-      <c r="J40" s="5" t="n">
+      <c r="J40" t="n">
         <v>66000</v>
       </c>
-      <c r="K40" s="4" t="n">
+      <c r="K40" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="4" t="n">
+      <c r="L40" t="n">
         <v>0</v>
       </c>
-      <c r="M40" s="5" t="n">
+      <c r="M40" t="n">
         <v>41700</v>
       </c>
-      <c r="N40" s="5" t="n">
+      <c r="N40" t="n">
         <v>41100</v>
       </c>
-      <c r="O40" s="5" t="n">
+      <c r="O40" t="n">
         <v>35800</v>
       </c>
-      <c r="P40" s="5" t="n">
+      <c r="P40" t="n">
         <v>5100</v>
       </c>
-      <c r="Q40" s="4" t="n">
+      <c r="Q40" t="n">
         <v>0</v>
       </c>
-      <c r="R40" s="4" t="inlineStr">
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>last_known (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>15100</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>12800</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>41700</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>41100</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>35800</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>34500</v>
+      </c>
+      <c r="N41" s="5" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="4" t="inlineStr">
         <is>
           <t>last_known (stale)</t>
         </is>

--- a/data/harga_sembako.xlsx
+++ b/data/harga_sembako.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X41"/>
+  <dimension ref="A1:X42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3460,63 +3460,115 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B41" t="n">
         <v>15100</v>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C41" t="n">
         <v>12800</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" t="n">
         <v>0</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" t="n">
         <v>0</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="F41" t="n">
         <v>0</v>
       </c>
-      <c r="G41" s="5" t="n">
+      <c r="G41" t="n">
         <v>41700</v>
       </c>
-      <c r="H41" s="5" t="n">
+      <c r="H41" t="n">
         <v>41100</v>
       </c>
-      <c r="I41" s="5" t="n">
+      <c r="I41" t="n">
         <v>35800</v>
       </c>
-      <c r="J41" s="5" t="n">
+      <c r="J41" t="n">
         <v>5100</v>
       </c>
-      <c r="K41" s="4" t="n">
+      <c r="K41" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="4" t="n">
+      <c r="L41" t="n">
         <v>0</v>
       </c>
-      <c r="M41" s="5" t="n">
+      <c r="M41" t="n">
         <v>34500</v>
       </c>
-      <c r="N41" s="5" t="n">
+      <c r="N41" t="n">
         <v>66000</v>
       </c>
-      <c r="O41" s="4" t="n">
+      <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="P41" s="4" t="n">
+      <c r="P41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" s="4" t="n">
+      <c r="Q41" t="n">
         <v>0</v>
       </c>
-      <c r="R41" s="4" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>last_known (stale)</t>
         </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>15100</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>12800</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>35800</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>34500</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_sembako.xlsx
+++ b/data/harga_sembako.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X42"/>
+  <dimension ref="A1:X43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3520,54 +3520,106 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n">
+      <c r="B42" t="n">
         <v>15100</v>
       </c>
-      <c r="C42" s="5" t="n">
+      <c r="C42" t="n">
         <v>12800</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" t="n">
         <v>0</v>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E42" t="n">
         <v>0</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="F42" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="4" t="n">
+      <c r="H42" t="n">
         <v>0</v>
       </c>
-      <c r="I42" s="5" t="n">
+      <c r="I42" t="n">
         <v>35800</v>
       </c>
-      <c r="J42" s="5" t="n">
+      <c r="J42" t="n">
         <v>5100</v>
       </c>
-      <c r="K42" s="4" t="n">
+      <c r="K42" t="n">
         <v>0</v>
       </c>
-      <c r="M42" s="5" t="n">
+      <c r="M42" t="n">
         <v>34500</v>
       </c>
-      <c r="N42" s="5" t="n">
+      <c r="N42" t="n">
         <v>66000</v>
       </c>
-      <c r="O42" s="4" t="n">
+      <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="P42" s="4" t="n">
+      <c r="P42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" s="4" t="n">
+      <c r="Q42" t="n">
         <v>0</v>
       </c>
-      <c r="R42" s="4" t="n">
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>15100</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>12800</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>35800</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>34500</v>
+      </c>
+      <c r="N43" s="5" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/harga_sembako.xlsx
+++ b/data/harga_sembako.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X43"/>
+  <dimension ref="A1:X46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3572,54 +3572,210 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n">
+      <c r="B43" t="n">
         <v>15100</v>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C43" t="n">
         <v>12800</v>
       </c>
-      <c r="D43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="5" t="n">
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>35800</v>
       </c>
-      <c r="J43" s="5" t="n">
+      <c r="J43" t="n">
         <v>5100</v>
       </c>
-      <c r="K43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="5" t="n">
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
         <v>34500</v>
       </c>
-      <c r="N43" s="5" t="n">
+      <c r="N43" t="n">
         <v>66000</v>
       </c>
-      <c r="O43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="4" t="n">
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>15100</v>
+      </c>
+      <c r="C44" t="n">
+        <v>12800</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>35800</v>
+      </c>
+      <c r="J44" t="n">
+        <v>5100</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>34500</v>
+      </c>
+      <c r="N44" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>15100</v>
+      </c>
+      <c r="C45" t="n">
+        <v>12800</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>35800</v>
+      </c>
+      <c r="J45" t="n">
+        <v>5100</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>34500</v>
+      </c>
+      <c r="N45" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>15100</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>12800</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>35800</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="K46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>34500</v>
+      </c>
+      <c r="N46" s="5" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/harga_sembako.xlsx
+++ b/data/harga_sembako.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X46"/>
+  <dimension ref="A1:X48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3728,56 +3728,121 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="B46" s="5" t="n">
+      <c r="B46" t="n">
         <v>15100</v>
       </c>
-      <c r="C46" s="5" t="n">
+      <c r="C46" t="n">
         <v>12800</v>
       </c>
-      <c r="D46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="5" t="n">
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
         <v>35800</v>
       </c>
-      <c r="J46" s="5" t="n">
+      <c r="J46" t="n">
         <v>5100</v>
       </c>
-      <c r="K46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="5" t="n">
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
         <v>34500</v>
       </c>
-      <c r="N46" s="5" t="n">
+      <c r="N46" t="n">
         <v>66000</v>
       </c>
-      <c r="O46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>15100</v>
+      </c>
+      <c r="C47" t="n">
+        <v>12800</v>
+      </c>
+      <c r="I47" t="n">
+        <v>35800</v>
+      </c>
+      <c r="J47" t="n">
+        <v>5100</v>
+      </c>
+      <c r="M47" t="n">
+        <v>34500</v>
+      </c>
+      <c r="N47" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>15100</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>12800</v>
+      </c>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="n"/>
+      <c r="H48" s="4" t="n"/>
+      <c r="I48" s="5" t="n">
+        <v>35800</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="K48" s="4" t="n"/>
+      <c r="M48" s="5" t="n">
+        <v>34500</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O48" s="4" t="n"/>
+      <c r="P48" s="4" t="n"/>
+      <c r="Q48" s="4" t="n"/>
+      <c r="R48" s="4" t="n"/>
+      <c r="S48" s="4" t="n"/>
+      <c r="T48" s="4" t="n"/>
+      <c r="U48" s="4" t="n"/>
+      <c r="V48" s="4" t="n"/>
+      <c r="W48" s="4" t="n"/>
+      <c r="X48" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/harga_sembako.xlsx
+++ b/data/harga_sembako.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X48"/>
+  <dimension ref="A1:X56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3805,44 +3805,244 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="B48" s="5" t="n">
+      <c r="B48" t="n">
         <v>15100</v>
       </c>
-      <c r="C48" s="5" t="n">
+      <c r="C48" t="n">
         <v>12800</v>
       </c>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-      <c r="F48" s="4" t="n"/>
-      <c r="H48" s="4" t="n"/>
-      <c r="I48" s="5" t="n">
+      <c r="I48" t="n">
         <v>35800</v>
       </c>
-      <c r="J48" s="5" t="n">
+      <c r="J48" t="n">
         <v>5100</v>
       </c>
-      <c r="K48" s="4" t="n"/>
-      <c r="M48" s="5" t="n">
+      <c r="M48" t="n">
         <v>34500</v>
       </c>
-      <c r="N48" s="5" t="n">
+      <c r="N48" t="n">
         <v>66000</v>
       </c>
-      <c r="O48" s="4" t="n"/>
-      <c r="P48" s="4" t="n"/>
-      <c r="Q48" s="4" t="n"/>
-      <c r="R48" s="4" t="n"/>
-      <c r="S48" s="4" t="n"/>
-      <c r="T48" s="4" t="n"/>
-      <c r="U48" s="4" t="n"/>
-      <c r="V48" s="4" t="n"/>
-      <c r="W48" s="4" t="n"/>
-      <c r="X48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>15100</v>
+      </c>
+      <c r="C49" t="n">
+        <v>12800</v>
+      </c>
+      <c r="I49" t="n">
+        <v>35800</v>
+      </c>
+      <c r="J49" t="n">
+        <v>5100</v>
+      </c>
+      <c r="M49" t="n">
+        <v>34500</v>
+      </c>
+      <c r="N49" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>15100</v>
+      </c>
+      <c r="C50" t="n">
+        <v>12800</v>
+      </c>
+      <c r="I50" t="n">
+        <v>35800</v>
+      </c>
+      <c r="J50" t="n">
+        <v>5100</v>
+      </c>
+      <c r="M50" t="n">
+        <v>34500</v>
+      </c>
+      <c r="N50" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>15100</v>
+      </c>
+      <c r="C51" t="n">
+        <v>12800</v>
+      </c>
+      <c r="I51" t="n">
+        <v>35800</v>
+      </c>
+      <c r="J51" t="n">
+        <v>5100</v>
+      </c>
+      <c r="M51" t="n">
+        <v>34500</v>
+      </c>
+      <c r="N51" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>15100</v>
+      </c>
+      <c r="C52" t="n">
+        <v>12800</v>
+      </c>
+      <c r="I52" t="n">
+        <v>35800</v>
+      </c>
+      <c r="J52" t="n">
+        <v>5100</v>
+      </c>
+      <c r="M52" t="n">
+        <v>34500</v>
+      </c>
+      <c r="N52" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>15100</v>
+      </c>
+      <c r="C53" t="n">
+        <v>12800</v>
+      </c>
+      <c r="I53" t="n">
+        <v>35800</v>
+      </c>
+      <c r="J53" t="n">
+        <v>5100</v>
+      </c>
+      <c r="M53" t="n">
+        <v>34500</v>
+      </c>
+      <c r="N53" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>15100</v>
+      </c>
+      <c r="C54" t="n">
+        <v>12800</v>
+      </c>
+      <c r="I54" t="n">
+        <v>35800</v>
+      </c>
+      <c r="J54" t="n">
+        <v>5100</v>
+      </c>
+      <c r="M54" t="n">
+        <v>34500</v>
+      </c>
+      <c r="N54" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>15100</v>
+      </c>
+      <c r="C55" t="n">
+        <v>12800</v>
+      </c>
+      <c r="I55" t="n">
+        <v>35800</v>
+      </c>
+      <c r="J55" t="n">
+        <v>5100</v>
+      </c>
+      <c r="M55" t="n">
+        <v>34500</v>
+      </c>
+      <c r="N55" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>15100</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>12800</v>
+      </c>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="4" t="n"/>
+      <c r="F56" s="4" t="n"/>
+      <c r="H56" s="4" t="n"/>
+      <c r="I56" s="5" t="n">
+        <v>35800</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="K56" s="4" t="n"/>
+      <c r="M56" s="5" t="n">
+        <v>34500</v>
+      </c>
+      <c r="N56" s="5" t="n">
+        <v>66000</v>
+      </c>
+      <c r="O56" s="4" t="n"/>
+      <c r="P56" s="4" t="n"/>
+      <c r="Q56" s="4" t="n"/>
+      <c r="R56" s="4" t="n"/>
+      <c r="S56" s="4" t="n"/>
+      <c r="T56" s="4" t="n"/>
+      <c r="U56" s="4" t="n"/>
+      <c r="V56" s="4" t="n"/>
+      <c r="W56" s="4" t="n"/>
+      <c r="X56" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
